--- a/survey_templates/042_evening_availability_survey--survey_templates.xlsx
+++ b/survey_templates/042_evening_availability_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1010,8 +1010,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_3.1,_'name':_'monday'}</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 3.1, 'name': 'Monday'}</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_3.2,_'name':_'tuesday'}</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 3.2, 'name': 'Tuesday'}</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3.3,_'name':_'wednesday'}</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3.3, 'name': 'Wednesday'}</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
@@ -1090,12 +1090,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_3.4,_'name':_'thursday'}</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 3.4, 'name': 'Thursday'}</t>
+          <t>Thursday</t>
         </is>
       </c>
     </row>
@@ -1107,12 +1107,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3.5,_'name':_'friday'}</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3.5, 'name': 'Friday'}</t>
+          <t>Friday</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3.6,_'name':_'saturday'}</t>
+          <t>saturday</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3.6, 'name': 'Saturday'}</t>
+          <t>Saturday</t>
         </is>
       </c>
     </row>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3.7,_'name':_'sunday'}</t>
+          <t>sunday</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3.7, 'name': 'Sunday'}</t>
+          <t>Sunday</t>
         </is>
       </c>
     </row>
@@ -1158,12 +1158,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_7.1,_'name':_'monday'}</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 7.1, 'name': 'Monday'}</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_7.2,_'name':_'tuesday'}</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 7.2, 'name': 'Tuesday'}</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_7.3,_'name':_'wednesday'}</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 7.3, 'name': 'Wednesday'}</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_7.4,_'name':_'thursday'}</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 7.4, 'name': 'Thursday'}</t>
+          <t>Thursday</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_7.5,_'name':_'friday'}</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 7.5, 'name': 'Friday'}</t>
+          <t>Friday</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_7.6,_'name':_'saturday'}</t>
+          <t>saturday</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 7.6, 'name': 'Saturday'}</t>
+          <t>Saturday</t>
         </is>
       </c>
     </row>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_7.7,_'name':_'sunday'}</t>
+          <t>sunday</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 7.7, 'name': 'Sunday'}</t>
+          <t>Sunday</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_10.1,_'name':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 10.1, 'name': 'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
     </row>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_10.2,_'name':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 10.2, 'name': 'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
     </row>
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_10.3,_'name':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 10.3, 'name': 'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
     </row>
@@ -1328,12 +1328,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_10.4,_'name':_'as_needed'}</t>
+          <t>as_needed</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 10.4, 'name': 'as_needed'}</t>
+          <t>as needed</t>
         </is>
       </c>
     </row>
@@ -1345,12 +1345,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_11.1,_'name':_'video_call'}</t>
+          <t>video_call</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 11.1, 'name': 'Video Call'}</t>
+          <t>Video Call</t>
         </is>
       </c>
     </row>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_11.2,_'name':_'phone_call'}</t>
+          <t>phone_call</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 11.2, 'name': 'Phone Call'}</t>
+          <t>Phone Call</t>
         </is>
       </c>
     </row>
@@ -1379,12 +1379,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_11.3,_'name':_'in_person'}</t>
+          <t>in_person</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 11.3, 'name': 'In Person'}</t>
+          <t>In Person</t>
         </is>
       </c>
     </row>
@@ -1396,12 +1396,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_12.1,_'name':_'15_minutes'}</t>
+          <t>15_minutes</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 12.1, 'name': '15 minutes'}</t>
+          <t>15 minutes</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_12.2,_'name':_'30_minutes'}</t>
+          <t>30_minutes</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 12.2, 'name': '30 minutes'}</t>
+          <t>30 minutes</t>
         </is>
       </c>
     </row>
@@ -1430,12 +1430,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_12.3,_'name':_'60_minutes'}</t>
+          <t>60_minutes</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 12.3, 'name': '60 minutes'}</t>
+          <t>60 minutes</t>
         </is>
       </c>
     </row>
@@ -1447,12 +1447,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_12.4,_'name':_'90_minutes'}</t>
+          <t>90_minutes</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 12.4, 'name': '90 minutes'}</t>
+          <t>90 minutes</t>
         </is>
       </c>
     </row>
@@ -1464,12 +1464,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_12.5,_'name':_'120_minutes'}</t>
+          <t>120_minutes</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 12.5, 'name': '120 minutes'}</t>
+          <t>120 minutes</t>
         </is>
       </c>
     </row>
@@ -1481,12 +1481,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_13.1,_'name':_'15_minutes'}</t>
+          <t>15_minutes</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 13.1, 'name': '15 minutes'}</t>
+          <t>15 minutes</t>
         </is>
       </c>
     </row>
@@ -1498,12 +1498,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_13.2,_'name':_'30_minutes'}</t>
+          <t>30_minutes</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 13.2, 'name': '30 minutes'}</t>
+          <t>30 minutes</t>
         </is>
       </c>
     </row>
@@ -1515,12 +1515,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_13.3,_'name':_'60_minutes'}</t>
+          <t>60_minutes</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 13.3, 'name': '60 minutes'}</t>
+          <t>60 minutes</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_13.4,_'name':_'90_minutes'}</t>
+          <t>90_minutes</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 13.4, 'name': '90 minutes'}</t>
+          <t>90 minutes</t>
         </is>
       </c>
     </row>
@@ -1549,12 +1549,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_13.5,_'name':_'120_minutes'}</t>
+          <t>120_minutes</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 13.5, 'name': '120 minutes'}</t>
+          <t>120 minutes</t>
         </is>
       </c>
     </row>
@@ -1566,12 +1566,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_16.1,_'name':_'monday'}</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 16.1, 'name': 'Monday'}</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
@@ -1583,12 +1583,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_16.2,_'name':_'tuesday'}</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 16.2, 'name': 'Tuesday'}</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
@@ -1600,12 +1600,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_16.3,_'name':_'wednesday'}</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 16.3, 'name': 'Wednesday'}</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
@@ -1617,12 +1617,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_16.4,_'name':_'thursday'}</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 16.4, 'name': 'Thursday'}</t>
+          <t>Thursday</t>
         </is>
       </c>
     </row>
@@ -1634,12 +1634,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_16.5,_'name':_'friday'}</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 16.5, 'name': 'Friday'}</t>
+          <t>Friday</t>
         </is>
       </c>
     </row>
@@ -1651,12 +1651,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_16.6,_'name':_'saturday'}</t>
+          <t>saturday</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 16.6, 'name': 'Saturday'}</t>
+          <t>Saturday</t>
         </is>
       </c>
     </row>
@@ -1668,12 +1668,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_16.7,_'name':_'sunday'}</t>
+          <t>sunday</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 16.7, 'name': 'Sunday'}</t>
+          <t>Sunday</t>
         </is>
       </c>
     </row>
@@ -1685,12 +1685,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_17.1,_'name':_'monday'}</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 17.1, 'name': 'Monday'}</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
@@ -1702,12 +1702,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_17.2,_'name':_'tuesday'}</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 17.2, 'name': 'Tuesday'}</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
@@ -1719,12 +1719,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_17.3,_'name':_'wednesday'}</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 17.3, 'name': 'Wednesday'}</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
@@ -1736,12 +1736,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'id':_17.4,_'name':_'thursday'}</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'id': 17.4, 'name': 'Thursday'}</t>
+          <t>Thursday</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'id':_17.5,_'name':_'friday'}</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'id': 17.5, 'name': 'Friday'}</t>
+          <t>Friday</t>
         </is>
       </c>
     </row>
@@ -1770,12 +1770,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'id':_17.6,_'name':_'saturday'}</t>
+          <t>saturday</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'id': 17.6, 'name': 'Saturday'}</t>
+          <t>Saturday</t>
         </is>
       </c>
     </row>
@@ -1787,12 +1787,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'id':_17.7,_'name':_'sunday'}</t>
+          <t>sunday</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'id': 17.7, 'name': 'Sunday'}</t>
+          <t>Sunday</t>
         </is>
       </c>
     </row>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'id':_18.1,_'name':_'once'}</t>
+          <t>once</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'id': 18.1, 'name': 'once'}</t>
+          <t>once</t>
         </is>
       </c>
     </row>
@@ -1821,12 +1821,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'id':_18.2,_'name':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'id': 18.2, 'name': 'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
     </row>
@@ -1838,12 +1838,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'id':_18.3,_'name':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'id': 18.3, 'name': 'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
     </row>
@@ -1855,12 +1855,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'id':_19.1,_'name':_'once'}</t>
+          <t>once</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'id': 19.1, 'name': 'once'}</t>
+          <t>once</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'id':_19.2,_'name':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'id': 19.2, 'name': 'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
     </row>
@@ -1889,12 +1889,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'id':_19.3,_'name':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'id': 19.3, 'name': 'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
     </row>
